--- a/outputs/04_individual_models/mmse_feature_selection.xlsx
+++ b/outputs/04_individual_models/mmse_feature_selection.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="83">
   <si>
     <t>field</t>
   </si>
@@ -63,7 +63,7 @@
     <t>note</t>
   </si>
   <si>
-    <t>MMSE only</t>
+    <t>MMSE</t>
   </si>
   <si>
     <t>&gt;= 50%</t>
@@ -127,9 +127,6 @@
   </si>
   <si>
     <t>MMMONTH</t>
-  </si>
-  <si>
-    <t>MMSE</t>
   </si>
   <si>
     <t>item</t>
@@ -785,13 +782,13 @@
         <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F2">
         <v>-0.166036</v>
@@ -800,7 +797,7 @@
         <v>0.166036</v>
       </c>
       <c r="H2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -817,13 +814,13 @@
         <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F3">
         <v>-0.154364</v>
@@ -832,7 +829,7 @@
         <v>0.154364</v>
       </c>
       <c r="H3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -849,13 +846,13 @@
         <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F4">
         <v>-0.104646</v>
@@ -864,7 +861,7 @@
         <v>0.104646</v>
       </c>
       <c r="H4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -881,13 +878,13 @@
         <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F5">
         <v>-0.08735</v>
@@ -896,7 +893,7 @@
         <v>0.08735</v>
       </c>
       <c r="H5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -913,13 +910,13 @@
         <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F6">
         <v>-0.08389099999999999</v>
@@ -928,7 +925,7 @@
         <v>0.08389099999999999</v>
       </c>
       <c r="H6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -945,13 +942,13 @@
         <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F7">
         <v>-0.063719</v>
@@ -960,7 +957,7 @@
         <v>0.063719</v>
       </c>
       <c r="H7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -977,13 +974,13 @@
         <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F8">
         <v>-0.03563</v>
@@ -992,7 +989,7 @@
         <v>0.03563</v>
       </c>
       <c r="H8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -1009,13 +1006,13 @@
         <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F9">
         <v>-0.033578</v>
@@ -1024,7 +1021,7 @@
         <v>0.033578</v>
       </c>
       <c r="H9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -1041,13 +1038,13 @@
         <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F10">
         <v>-0.017784</v>
@@ -1056,7 +1053,7 @@
         <v>0.017784</v>
       </c>
       <c r="H10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -1094,16 +1091,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E2">
         <v>82.90000000000001</v>
@@ -1111,16 +1108,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E3">
         <v>100</v>
@@ -1128,16 +1125,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E4">
         <v>100</v>
@@ -1145,16 +1142,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E5">
         <v>100</v>
@@ -1162,16 +1159,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E6">
         <v>100</v>
@@ -1179,16 +1176,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E7">
         <v>100</v>
@@ -1196,16 +1193,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E8">
         <v>82.90000000000001</v>
@@ -1213,16 +1210,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E9">
         <v>100</v>
@@ -1230,16 +1227,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E10">
         <v>100</v>
@@ -1247,16 +1244,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E11">
         <v>100</v>
@@ -1264,16 +1261,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E12">
         <v>100</v>
@@ -1281,16 +1278,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E13">
         <v>100</v>
@@ -1298,16 +1295,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E14">
         <v>82.90000000000001</v>
@@ -1315,16 +1312,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E15">
         <v>82.90000000000001</v>
@@ -1332,16 +1329,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E16">
         <v>100</v>
@@ -1349,16 +1346,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E17">
         <v>82.90000000000001</v>
@@ -1366,16 +1363,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E18">
         <v>100</v>
@@ -1383,16 +1380,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E19">
         <v>100</v>
@@ -1400,16 +1397,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E20">
         <v>100</v>
@@ -1417,16 +1414,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E21">
         <v>100</v>
@@ -1434,16 +1431,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E22">
         <v>82.90000000000001</v>
@@ -1451,16 +1448,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E23">
         <v>100</v>
@@ -1468,16 +1465,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E24">
         <v>100</v>
@@ -1485,16 +1482,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E25">
         <v>100</v>
@@ -1502,16 +1499,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E26">
         <v>100</v>
@@ -1519,16 +1516,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E27">
         <v>100</v>
@@ -1536,16 +1533,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E28">
         <v>100</v>
@@ -1553,16 +1550,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E29">
         <v>100</v>
@@ -1583,21 +1580,21 @@
         <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="B2">
         <v>37</v>
@@ -1630,24 +1627,24 @@
         <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C2">
         <v>6</v>
@@ -1664,10 +1661,10 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C3">
         <v>30</v>
@@ -1684,10 +1681,10 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1746,13 +1743,13 @@
         <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2">
         <v>-0.166036</v>
@@ -1761,7 +1758,7 @@
         <v>0.166036</v>
       </c>
       <c r="G2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -1775,13 +1772,13 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E3">
         <v>-0.154364</v>
@@ -1790,7 +1787,7 @@
         <v>0.154364</v>
       </c>
       <c r="G3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -1804,13 +1801,13 @@
         <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E4">
         <v>-0.104646</v>
@@ -1819,7 +1816,7 @@
         <v>0.104646</v>
       </c>
       <c r="G4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -1833,13 +1830,13 @@
         <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E5">
         <v>-0.08735</v>
@@ -1848,7 +1845,7 @@
         <v>0.08735</v>
       </c>
       <c r="G5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -1862,13 +1859,13 @@
         <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E6">
         <v>-0.08389099999999999</v>
@@ -1877,7 +1874,7 @@
         <v>0.08389099999999999</v>
       </c>
       <c r="G6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -1891,13 +1888,13 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E7">
         <v>-0.063719</v>
@@ -1906,7 +1903,7 @@
         <v>0.063719</v>
       </c>
       <c r="G7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -1920,13 +1917,13 @@
         <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E8">
         <v>-0.03563</v>
@@ -1935,7 +1932,7 @@
         <v>0.03563</v>
       </c>
       <c r="G8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -1949,13 +1946,13 @@
         <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E9">
         <v>-0.033578</v>
@@ -1964,7 +1961,7 @@
         <v>0.033578</v>
       </c>
       <c r="G9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -1978,13 +1975,13 @@
         <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E10">
         <v>-0.017784</v>
@@ -1993,7 +1990,7 @@
         <v>0.017784</v>
       </c>
       <c r="G10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -2004,16 +2001,16 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -2022,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -2033,16 +2030,16 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -2051,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -2062,16 +2059,16 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -2080,7 +2077,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -2091,16 +2088,16 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -2109,7 +2106,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -2120,16 +2117,16 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -2138,7 +2135,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -2149,16 +2146,16 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -2167,7 +2164,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -2178,16 +2175,16 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -2196,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -2207,16 +2204,16 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -2225,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -2236,16 +2233,16 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2254,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -2265,16 +2262,16 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2283,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -2294,16 +2291,16 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -2312,7 +2309,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -2323,16 +2320,16 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -2341,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -2352,16 +2349,16 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2370,7 +2367,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -2381,16 +2378,16 @@
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2399,7 +2396,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -2410,16 +2407,16 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2428,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -2439,16 +2436,16 @@
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2457,7 +2454,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -2468,16 +2465,16 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2486,7 +2483,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -2497,16 +2494,16 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D28" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2515,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -2526,16 +2523,16 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2544,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -2555,16 +2552,16 @@
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2573,7 +2570,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -2584,16 +2581,16 @@
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2602,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -2613,16 +2610,16 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D32" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2631,7 +2628,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -2642,16 +2639,16 @@
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D33" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2660,7 +2657,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -2671,16 +2668,16 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2689,7 +2686,7 @@
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -2700,16 +2697,16 @@
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B35" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2718,7 +2715,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -2729,16 +2726,16 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D36" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2747,7 +2744,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -2758,16 +2755,16 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B37" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C37" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2776,7 +2773,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -2787,16 +2784,16 @@
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D38" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -2805,7 +2802,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H38">
         <v>0</v>
